--- a/tests/scripts/golden_snapshot/visual_report.xlsx
+++ b/tests/scripts/golden_snapshot/visual_report.xlsx
@@ -12128,7 +12128,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12176,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D73" t="b">
